--- a/result_analyze.xlsx
+++ b/result_analyze.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,6 +692,843 @@
         <v>189</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>03-04-22</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>35689</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7129</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17147</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5558</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5136</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>422</v>
+      </c>
+      <c r="I9" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>03-05-00</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>88</v>
+      </c>
+      <c r="C10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" t="n">
+        <v>53</v>
+      </c>
+      <c r="E10" t="n">
+        <v>14</v>
+      </c>
+      <c r="F10" t="n">
+        <v>12</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>03-05-00</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>38050</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9492</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16844</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5736</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5373</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5229</v>
+      </c>
+      <c r="H11" t="n">
+        <v>363</v>
+      </c>
+      <c r="I11" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>03-05-01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>36858</v>
+      </c>
+      <c r="C12" t="n">
+        <v>9534</v>
+      </c>
+      <c r="D12" t="n">
+        <v>15860</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6317</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5913</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5762</v>
+      </c>
+      <c r="H12" t="n">
+        <v>404</v>
+      </c>
+      <c r="I12" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>03-05-02</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>35959</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9221</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15226</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6211</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5867</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5739</v>
+      </c>
+      <c r="H13" t="n">
+        <v>344</v>
+      </c>
+      <c r="I13" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>03-05-03</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>36349</v>
+      </c>
+      <c r="C14" t="n">
+        <v>8742</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16068</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6112</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5724</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5605</v>
+      </c>
+      <c r="H14" t="n">
+        <v>388</v>
+      </c>
+      <c r="I14" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>03-05-04</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>35164</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8195</v>
+      </c>
+      <c r="D15" t="n">
+        <v>15564</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6048</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5617</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5470</v>
+      </c>
+      <c r="H15" t="n">
+        <v>431</v>
+      </c>
+      <c r="I15" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>03-05-05</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>34829</v>
+      </c>
+      <c r="C16" t="n">
+        <v>8140</v>
+      </c>
+      <c r="D16" t="n">
+        <v>14839</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6014</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5570</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5436</v>
+      </c>
+      <c r="H16" t="n">
+        <v>444</v>
+      </c>
+      <c r="I16" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>03-05-06</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>37369</v>
+      </c>
+      <c r="C17" t="n">
+        <v>9123</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16506</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6287</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5864</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5731</v>
+      </c>
+      <c r="H17" t="n">
+        <v>423</v>
+      </c>
+      <c r="I17" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>03-05-07</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>36662</v>
+      </c>
+      <c r="C18" t="n">
+        <v>9810</v>
+      </c>
+      <c r="D18" t="n">
+        <v>15121</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6525</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6101</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5980</v>
+      </c>
+      <c r="H18" t="n">
+        <v>424</v>
+      </c>
+      <c r="I18" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>03-05-08</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>36165</v>
+      </c>
+      <c r="C19" t="n">
+        <v>9524</v>
+      </c>
+      <c r="D19" t="n">
+        <v>15071</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6230</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5873</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5721</v>
+      </c>
+      <c r="H19" t="n">
+        <v>357</v>
+      </c>
+      <c r="I19" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>03-05-09</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>36453</v>
+      </c>
+      <c r="C20" t="n">
+        <v>9202</v>
+      </c>
+      <c r="D20" t="n">
+        <v>15716</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6223</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5770</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5636</v>
+      </c>
+      <c r="H20" t="n">
+        <v>453</v>
+      </c>
+      <c r="I20" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>03-05-10</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>41201</v>
+      </c>
+      <c r="C21" t="n">
+        <v>14760</v>
+      </c>
+      <c r="D21" t="n">
+        <v>14090</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7817</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7410</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7176</v>
+      </c>
+      <c r="H21" t="n">
+        <v>407</v>
+      </c>
+      <c r="I21" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>03-05-11</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>40569</v>
+      </c>
+      <c r="C22" t="n">
+        <v>13697</v>
+      </c>
+      <c r="D22" t="n">
+        <v>14493</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7605</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7177</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6978</v>
+      </c>
+      <c r="H22" t="n">
+        <v>428</v>
+      </c>
+      <c r="I22" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>03-05-12</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>39249</v>
+      </c>
+      <c r="C23" t="n">
+        <v>11504</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15131</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7064</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6613</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6446</v>
+      </c>
+      <c r="H23" t="n">
+        <v>451</v>
+      </c>
+      <c r="I23" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>03-05-14</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>37230</v>
+      </c>
+      <c r="C24" t="n">
+        <v>9855</v>
+      </c>
+      <c r="D24" t="n">
+        <v>15217</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9406</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5753</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5604</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3653</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>03-05-15</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>36889</v>
+      </c>
+      <c r="C25" t="n">
+        <v>10360</v>
+      </c>
+      <c r="D25" t="n">
+        <v>14773</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9645</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5865</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5724</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3780</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>03-05-16</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>36514</v>
+      </c>
+      <c r="C26" t="n">
+        <v>9136</v>
+      </c>
+      <c r="D26" t="n">
+        <v>15380</v>
+      </c>
+      <c r="E26" t="n">
+        <v>9303</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5586</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5444</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3717</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>03-05-17</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>47054</v>
+      </c>
+      <c r="C27" t="n">
+        <v>16448</v>
+      </c>
+      <c r="D27" t="n">
+        <v>19779</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15570</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9496</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8866</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6074</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>03-05-18</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>38527</v>
+      </c>
+      <c r="C28" t="n">
+        <v>10157</v>
+      </c>
+      <c r="D28" t="n">
+        <v>16091</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9903</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6135</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3768</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>03-05-19</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>33560</v>
+      </c>
+      <c r="C29" t="n">
+        <v>9568</v>
+      </c>
+      <c r="D29" t="n">
+        <v>13658</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8382</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5321</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5168</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3061</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>03-05-20</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>41038</v>
+      </c>
+      <c r="C30" t="n">
+        <v>14244</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16679</v>
+      </c>
+      <c r="E30" t="n">
+        <v>13356</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8541</v>
+      </c>
+      <c r="G30" t="n">
+        <v>8147</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4815</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>03-05-20</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>41038</v>
+      </c>
+      <c r="C31" t="n">
+        <v>14244</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16679</v>
+      </c>
+      <c r="E31" t="n">
+        <v>13356</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8541</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8147</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4815</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>03-05-20</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>41038</v>
+      </c>
+      <c r="C32" t="n">
+        <v>14244</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16679</v>
+      </c>
+      <c r="E32" t="n">
+        <v>13356</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8541</v>
+      </c>
+      <c r="G32" t="n">
+        <v>8147</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4815</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>03-05-20</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>41038</v>
+      </c>
+      <c r="C33" t="n">
+        <v>14244</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16679</v>
+      </c>
+      <c r="E33" t="n">
+        <v>13356</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8541</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8147</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4815</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>03-05-21</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33195</v>
+      </c>
+      <c r="C34" t="n">
+        <v>8624</v>
+      </c>
+      <c r="D34" t="n">
+        <v>13826</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8343</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5246</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5124</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3097</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>03-05-21</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>33195</v>
+      </c>
+      <c r="C35" t="n">
+        <v>8624</v>
+      </c>
+      <c r="D35" t="n">
+        <v>13826</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8343</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5246</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5124</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3097</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
